--- a/media/exports/reports/2025-12/funding.xlsx
+++ b/media/exports/reports/2025-12/funding.xlsx
@@ -24,45 +24,54 @@
     <numFmt numFmtId="164" formatCode="0&quot;¢&quot;;[Red](0&quot;¢&quot;)"/>
     <numFmt numFmtId="165" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
@@ -95,40 +104,40 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -875,8 +884,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 funding.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1048,8 +1057,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 funding.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2535,8 +2544,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Community Services Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 funding.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2025-12/funding.xlsx
+++ b/media/exports/reports/2025-12/funding.xlsx
@@ -24,7 +24,7 @@
     <numFmt numFmtId="164" formatCode="0&quot;¢&quot;;[Red](0&quot;¢&quot;)"/>
     <numFmt numFmtId="165" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Roboto"/>
       <sz val="11"/>
@@ -75,6 +75,10 @@
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
+    <font>
+      <name val="Roboto"/>
+      <color rgb="005F6F63"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -106,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,6 +127,8 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
@@ -138,6 +144,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -506,7 +515,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -748,126 +757,192 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Headline number</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>Compared with</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Cheapest to raise: Grants</t>
+        </is>
+      </c>
+      <c r="B43" s="8">
+        <f>Workings!B30</f>
+        <v/>
+      </c>
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>per $1 raised in December</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Dearest to raise: Fundraising events</t>
+        </is>
+      </c>
+      <c r="B44" s="8">
+        <f>Workings!B44</f>
+        <v/>
+      </c>
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>per $1 raised in December</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Raised, year to date</t>
+        </is>
+      </c>
+      <c r="B45" s="11">
+        <f>Workings!B53</f>
+        <v/>
+      </c>
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>Jul to Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Financial year to date (Jul to Dec 2025), by source</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr"/>
-      <c r="B43" s="7" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr"/>
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>Raised</t>
         </is>
       </c>
-      <c r="C43" s="7" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>Cost of raising it</t>
         </is>
       </c>
-      <c r="D43" s="7" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Left after costs</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>Cost per $1</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="10" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="12" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B44" s="11" t="inlineStr">
+      <c r="B49" s="13" t="inlineStr">
         <is>
           <t>$390,886</t>
         </is>
       </c>
-      <c r="C44" s="11" t="inlineStr">
+      <c r="C49" s="13" t="inlineStr">
         <is>
           <t>$42,600</t>
         </is>
       </c>
-      <c r="D44" s="11" t="inlineStr">
+      <c r="D49" s="13" t="inlineStr">
         <is>
           <t>$348,286</t>
         </is>
       </c>
-      <c r="E44" s="11" t="inlineStr">
+      <c r="E49" s="13" t="inlineStr">
         <is>
           <t>11¢</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="10" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="12" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B45" s="11" t="inlineStr">
+      <c r="B50" s="13" t="inlineStr">
         <is>
           <t>$106,600</t>
         </is>
       </c>
-      <c r="C45" s="11" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>$16,300</t>
         </is>
       </c>
-      <c r="D45" s="11" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>$90,300</t>
         </is>
       </c>
-      <c r="E45" s="11" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>15¢</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="10" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="12" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B46" s="11" t="inlineStr">
+      <c r="B51" s="13" t="inlineStr">
         <is>
           <t>$43,000</t>
         </is>
       </c>
-      <c r="C46" s="11" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>$17,800</t>
         </is>
       </c>
-      <c r="D46" s="11" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>$25,200</t>
         </is>
       </c>
-      <c r="E46" s="11" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>41¢</t>
         </is>
       </c>
     </row>
-    <row r="47"/>
-    <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+    <row r="52"/>
+    <row r="53">
+      <c r="A53" s="14" t="inlineStr">
         <is>
           <t>Raised and left after costs, by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="49"/>
-    <row r="50"/>
+    <row r="54"/>
+    <row r="55"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:D5"/>
@@ -903,7 +978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
@@ -942,7 +1017,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
         <is>
           <t>Fundraising cost ÷ money raised, for each source, in cents</t>
         </is>
@@ -962,7 +1037,7 @@
           <t>Grants: cost (grant writing and reporting)</t>
         </is>
       </c>
-      <c r="B8" s="13" t="n">
+      <c r="B8" s="15" t="n">
         <v>7100</v>
       </c>
     </row>
@@ -972,7 +1047,7 @@
           <t>Grants: raised</t>
         </is>
       </c>
-      <c r="B9" s="13" t="n">
+      <c r="B9" s="15" t="n">
         <v>68793</v>
       </c>
     </row>
@@ -982,7 +1057,7 @@
           <t>Donations: cost (donor campaigns)</t>
         </is>
       </c>
-      <c r="B10" s="13" t="n">
+      <c r="B10" s="15" t="n">
         <v>4400</v>
       </c>
     </row>
@@ -992,7 +1067,7 @@
           <t>Donations: raised</t>
         </is>
       </c>
-      <c r="B11" s="13" t="n">
+      <c r="B11" s="15" t="n">
         <v>26100</v>
       </c>
     </row>
@@ -1002,7 +1077,7 @@
           <t>Fundraising events: cost (event costs)</t>
         </is>
       </c>
-      <c r="B12" s="13" t="n">
+      <c r="B12" s="15" t="n">
         <v>2600</v>
       </c>
     </row>
@@ -1012,7 +1087,7 @@
           <t>Fundraising events: raised</t>
         </is>
       </c>
-      <c r="B13" s="13" t="n">
+      <c r="B13" s="15" t="n">
         <v>6200</v>
       </c>
     </row>
@@ -1022,7 +1097,7 @@
           <t>Grants: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="16">
         <f>B8/B9*100</f>
         <v/>
       </c>
@@ -1033,25 +1108,324 @@
           <t>Donations: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="16">
         <f>B10/B11*100</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="inlineStr">
+      <c r="A16" s="17" t="inlineStr">
         <is>
           <t>Fundraising events: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="18">
         <f>B12/B13*100</f>
         <v/>
       </c>
     </row>
     <row r="17"/>
     <row r="18"/>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Cost to raise a dollar, by source, December 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
+          <t>Fundraising cost ÷ money raised, for each source, in cents</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr"/>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Grants: cost (grant writing and reporting)</t>
+        </is>
+      </c>
+      <c r="B22" s="15" t="n">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Grants: raised</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n">
+        <v>68793</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Donations: cost (donor campaigns)</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Donations: raised</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="n">
+        <v>26100</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fundraising events: cost (event costs)</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Fundraising events: raised</t>
+        </is>
+      </c>
+      <c r="B27" s="15" t="n">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Grants: cost per dollar raised</t>
+        </is>
+      </c>
+      <c r="B28" s="16">
+        <f>B22/B23*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Donations: cost per dollar raised</t>
+        </is>
+      </c>
+      <c r="B29" s="16">
+        <f>B24/B25*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Fundraising events: cost per dollar raised</t>
+        </is>
+      </c>
+      <c r="B30" s="18">
+        <f>B26/B27*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>Cost to raise a dollar, by source, December 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>Fundraising cost ÷ money raised, for each source, in cents</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr"/>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>Dec 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Grants: cost (grant writing and reporting)</t>
+        </is>
+      </c>
+      <c r="B36" s="15" t="n">
+        <v>7100</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Grants: raised</t>
+        </is>
+      </c>
+      <c r="B37" s="15" t="n">
+        <v>68793</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Donations: cost (donor campaigns)</t>
+        </is>
+      </c>
+      <c r="B38" s="15" t="n">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Donations: raised</t>
+        </is>
+      </c>
+      <c r="B39" s="15" t="n">
+        <v>26100</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Fundraising events: cost (event costs)</t>
+        </is>
+      </c>
+      <c r="B40" s="15" t="n">
+        <v>2600</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Fundraising events: raised</t>
+        </is>
+      </c>
+      <c r="B41" s="15" t="n">
+        <v>6200</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Grants: cost per dollar raised</t>
+        </is>
+      </c>
+      <c r="B42" s="16">
+        <f>B36/B37*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Donations: cost per dollar raised</t>
+        </is>
+      </c>
+      <c r="B43" s="16">
+        <f>B38/B39*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="17" t="inlineStr">
+        <is>
+          <t>Fundraising events: cost per dollar raised</t>
+        </is>
+      </c>
+      <c r="B44" s="18">
+        <f>B40/B41*100</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Raised, financial year to date (Jul to Dec 2025)</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="14" t="inlineStr">
+        <is>
+          <t>Grants + donations + fundraising events</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr"/>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>Year to date</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Grants, raised</t>
+        </is>
+      </c>
+      <c r="B50" s="15" t="n">
+        <v>390886</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Donations, raised</t>
+        </is>
+      </c>
+      <c r="B51" s="15" t="n">
+        <v>106600</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Fundraising events, raised</t>
+        </is>
+      </c>
+      <c r="B52" s="15" t="n">
+        <v>43000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="17" t="inlineStr">
+        <is>
+          <t>Raised, year to date</t>
+        </is>
+      </c>
+      <c r="B53" s="19">
+        <f>B50+B51+B52</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
   </sheetData>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
@@ -1064,6 +1438,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="32" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -1145,1396 +1522,1396 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="20" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="n">
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D6" s="15" t="n">
         <v>26600</v>
       </c>
-      <c r="E6" s="13" t="n">
+      <c r="E6" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F6" s="13">
+      <c r="F6" s="15">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="16">
         <f>IF(D6=0,"",E6/D6*100)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="n">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D7" s="15" t="n">
         <v>31800</v>
       </c>
-      <c r="E7" s="13" t="n">
+      <c r="E7" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F7" s="13">
+      <c r="F7" s="15">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="16">
         <f>IF(D7=0,"",E7/D7*100)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D8" s="13" t="n">
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
         <v>29700</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F8" s="13">
+      <c r="F8" s="15">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="16">
         <f>IF(D8=0,"",E8/D8*100)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="20" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="n">
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
         <v>62700</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F9" s="13">
+      <c r="F9" s="15">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="16">
         <f>IF(D9=0,"",E9/D9*100)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="n">
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
         <v>61700</v>
       </c>
-      <c r="E10" s="13" t="n">
+      <c r="E10" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F10" s="13">
+      <c r="F10" s="15">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="16">
         <f>IF(D10=0,"",E10/D10*100)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="20" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="n">
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
         <v>54500</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F11" s="13">
+      <c r="F11" s="15">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="16">
         <f>IF(D11=0,"",E11/D11*100)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="n">
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
         <v>61500</v>
       </c>
-      <c r="E12" s="13" t="n">
+      <c r="E12" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F12" s="13">
+      <c r="F12" s="15">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="16">
         <f>IF(D12=0,"",E12/D12*100)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="n">
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="n">
         <v>61700</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F13" s="13">
+      <c r="F13" s="15">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="16">
         <f>IF(D13=0,"",E13/D13*100)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="n">
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="n">
         <v>52200</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="15" t="n">
         <v>6500</v>
       </c>
-      <c r="F14" s="13">
+      <c r="F14" s="15">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="16">
         <f>IF(D14=0,"",E14/D14*100)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D15" s="13" t="n">
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
         <v>59063</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="15" t="n">
         <v>7100</v>
       </c>
-      <c r="F15" s="13">
+      <c r="F15" s="15">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="16">
         <f>IF(D15=0,"",E15/D15*100)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="n">
+      <c r="C16" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D16" s="15" t="n">
         <v>61544</v>
       </c>
-      <c r="E16" s="13" t="n">
+      <c r="E16" s="15" t="n">
         <v>7100</v>
       </c>
-      <c r="F16" s="13">
+      <c r="F16" s="15">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="16">
         <f>IF(D16=0,"",E16/D16*100)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="20" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D17" s="13" t="n">
+      <c r="C17" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D17" s="15" t="n">
         <v>62137</v>
       </c>
-      <c r="E17" s="13" t="n">
+      <c r="E17" s="15" t="n">
         <v>7100</v>
       </c>
-      <c r="F17" s="13">
+      <c r="F17" s="15">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="16">
         <f>IF(D17=0,"",E17/D17*100)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="n">
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="n">
         <v>69185</v>
       </c>
-      <c r="E18" s="13" t="n">
+      <c r="E18" s="15" t="n">
         <v>7100</v>
       </c>
-      <c r="F18" s="13">
+      <c r="F18" s="15">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="16">
         <f>IF(D18=0,"",E18/D18*100)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C19" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D19" s="13" t="n">
+      <c r="C19" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D19" s="15" t="n">
         <v>70164</v>
       </c>
-      <c r="E19" s="13" t="n">
+      <c r="E19" s="15" t="n">
         <v>7100</v>
       </c>
-      <c r="F19" s="13">
+      <c r="F19" s="15">
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="16">
         <f>IF(D19=0,"",E19/D19*100)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="20" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="20" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="n">
+      <c r="C20" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D20" s="15" t="n">
         <v>68793</v>
       </c>
-      <c r="E20" s="13" t="n">
+      <c r="E20" s="15" t="n">
         <v>7100</v>
       </c>
-      <c r="F20" s="13">
+      <c r="F20" s="15">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="16">
         <f>IF(D20=0,"",E20/D20*100)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="20" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C21" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="n">
+      <c r="C21" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="n">
         <v>15300</v>
       </c>
-      <c r="E21" s="13" t="n">
+      <c r="E21" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F21" s="13">
+      <c r="F21" s="15">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="16">
         <f>IF(D21=0,"",E21/D21*100)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C22" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="n">
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D22" s="15" t="n">
         <v>17700</v>
       </c>
-      <c r="E22" s="13" t="n">
+      <c r="E22" s="15" t="n">
         <v>3100</v>
       </c>
-      <c r="F22" s="13">
+      <c r="F22" s="15">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="16">
         <f>IF(D22=0,"",E22/D22*100)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C23" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D23" s="13" t="n">
+      <c r="C23" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n">
         <v>24700</v>
       </c>
-      <c r="E23" s="13" t="n">
+      <c r="E23" s="15" t="n">
         <v>4400</v>
       </c>
-      <c r="F23" s="13">
+      <c r="F23" s="15">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="14">
+      <c r="G23" s="16">
         <f>IF(D23=0,"",E23/D23*100)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C24" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="n">
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="n">
         <v>12400</v>
       </c>
-      <c r="E24" s="13" t="n">
+      <c r="E24" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F24" s="13">
+      <c r="F24" s="15">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="16">
         <f>IF(D24=0,"",E24/D24*100)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="20" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C25" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="n">
+      <c r="C25" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D25" s="15" t="n">
         <v>15600</v>
       </c>
-      <c r="E25" s="13" t="n">
+      <c r="E25" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F25" s="13">
+      <c r="F25" s="15">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="16">
         <f>IF(D25=0,"",E25/D25*100)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C26" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="n">
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="n">
         <v>15700</v>
       </c>
-      <c r="E26" s="13" t="n">
+      <c r="E26" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F26" s="13">
+      <c r="F26" s="15">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="16">
         <f>IF(D26=0,"",E26/D26*100)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="20" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C27" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="n">
+      <c r="C27" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n">
         <v>15700</v>
       </c>
-      <c r="E27" s="13" t="n">
+      <c r="E27" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F27" s="13">
+      <c r="F27" s="15">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="16">
         <f>IF(D27=0,"",E27/D27*100)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B28" s="20" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C28" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="n">
+      <c r="C28" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n">
         <v>15800</v>
       </c>
-      <c r="E28" s="13" t="n">
+      <c r="E28" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F28" s="13">
+      <c r="F28" s="15">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="16">
         <f>IF(D28=0,"",E28/D28*100)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B29" s="17" t="inlineStr">
+      <c r="B29" s="20" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C29" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="n">
+      <c r="C29" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="n">
         <v>38100</v>
       </c>
-      <c r="E29" s="13" t="n">
+      <c r="E29" s="15" t="n">
         <v>5500</v>
       </c>
-      <c r="F29" s="13">
+      <c r="F29" s="15">
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="16">
         <f>IF(D29=0,"",E29/D29*100)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="20" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C30" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="n">
+      <c r="C30" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="n">
         <v>13500</v>
       </c>
-      <c r="E30" s="13" t="n">
+      <c r="E30" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F30" s="13">
+      <c r="F30" s="15">
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="16">
         <f>IF(D30=0,"",E30/D30*100)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+      <c r="A31" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
+      <c r="B31" s="20" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C31" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="n">
+      <c r="C31" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="n">
         <v>16000</v>
       </c>
-      <c r="E31" s="13" t="n">
+      <c r="E31" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F31" s="13">
+      <c r="F31" s="15">
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="14">
+      <c r="G31" s="16">
         <f>IF(D31=0,"",E31/D31*100)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
+      <c r="A32" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B32" s="17" t="inlineStr">
+      <c r="B32" s="20" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C32" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="n">
+      <c r="C32" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="n">
         <v>16100</v>
       </c>
-      <c r="E32" s="13" t="n">
+      <c r="E32" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F32" s="13">
+      <c r="F32" s="15">
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="16">
         <f>IF(D32=0,"",E32/D32*100)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
+      <c r="B33" s="20" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C33" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="n">
+      <c r="C33" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D33" s="15" t="n">
         <v>16200</v>
       </c>
-      <c r="E33" s="13" t="n">
+      <c r="E33" s="15" t="n">
         <v>2200</v>
       </c>
-      <c r="F33" s="13">
+      <c r="F33" s="15">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="16">
         <f>IF(D33=0,"",E33/D33*100)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B34" s="17" t="inlineStr">
+      <c r="B34" s="20" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C34" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="n">
+      <c r="C34" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="n">
         <v>18700</v>
       </c>
-      <c r="E34" s="13" t="n">
+      <c r="E34" s="15" t="n">
         <v>3100</v>
       </c>
-      <c r="F34" s="13">
+      <c r="F34" s="15">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="14">
+      <c r="G34" s="16">
         <f>IF(D34=0,"",E34/D34*100)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="20" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B35" s="17" t="inlineStr">
+      <c r="B35" s="20" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C35" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="n">
+      <c r="C35" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D35" s="15" t="n">
         <v>26100</v>
       </c>
-      <c r="E35" s="13" t="n">
+      <c r="E35" s="15" t="n">
         <v>4400</v>
       </c>
-      <c r="F35" s="13">
+      <c r="F35" s="15">
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="16">
         <f>IF(D35=0,"",E35/D35*100)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B36" s="17" t="inlineStr">
+      <c r="B36" s="20" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="n">
+      <c r="C36" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="13" t="n">
+      <c r="E36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="13">
+      <c r="F36" s="15">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="16">
         <f>IF(D36=0,"",E36/D36*100)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
+      <c r="B37" s="20" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D37" s="13" t="n">
+      <c r="C37" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D37" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="13" t="n">
+      <c r="E37" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="13">
+      <c r="F37" s="15">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="16">
         <f>IF(D37=0,"",E37/D37*100)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B38" s="20" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C38" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="n">
+      <c r="C38" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D38" s="15" t="n">
         <v>6200</v>
       </c>
-      <c r="E38" s="13" t="n">
+      <c r="E38" s="15" t="n">
         <v>2600</v>
       </c>
-      <c r="F38" s="13">
+      <c r="F38" s="15">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="16">
         <f>IF(D38=0,"",E38/D38*100)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
+      <c r="B39" s="20" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="n">
+      <c r="C39" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D39" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="13" t="n">
+      <c r="E39" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="13">
+      <c r="F39" s="15">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="16">
         <f>IF(D39=0,"",E39/D39*100)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B40" s="17" t="inlineStr">
+      <c r="B40" s="20" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="n">
+      <c r="C40" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="13" t="n">
+      <c r="E40" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="13">
+      <c r="F40" s="15">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="16">
         <f>IF(D40=0,"",E40/D40*100)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B41" s="20" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="n">
+      <c r="C41" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D41" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="13" t="n">
+      <c r="E41" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="13">
+      <c r="F41" s="15">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="16">
         <f>IF(D41=0,"",E41/D41*100)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B42" s="17" t="inlineStr">
+      <c r="B42" s="20" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="n">
+      <c r="C42" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D42" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="13" t="n">
+      <c r="E42" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="13">
+      <c r="F42" s="15">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="16">
         <f>IF(D42=0,"",E42/D42*100)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B43" s="17" t="inlineStr">
+      <c r="B43" s="20" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D43" s="13" t="n">
+      <c r="C43" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D43" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="13" t="n">
+      <c r="E43" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="13">
+      <c r="F43" s="15">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="16">
         <f>IF(D43=0,"",E43/D43*100)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B44" s="17" t="inlineStr">
+      <c r="B44" s="20" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D44" s="13" t="n">
+      <c r="C44" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D44" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="13" t="n">
+      <c r="E44" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="13">
+      <c r="F44" s="15">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="14">
+      <c r="G44" s="16">
         <f>IF(D44=0,"",E44/D44*100)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B45" s="17" t="inlineStr">
+      <c r="B45" s="20" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D45" s="13" t="n">
+      <c r="C45" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D45" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="13" t="n">
+      <c r="E45" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="13">
+      <c r="F45" s="15">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="14">
+      <c r="G45" s="16">
         <f>IF(D45=0,"",E45/D45*100)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B46" s="20" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D46" s="13" t="n">
+      <c r="C46" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D46" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="13" t="n">
+      <c r="E46" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="13">
+      <c r="F46" s="15">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="14">
+      <c r="G46" s="16">
         <f>IF(D46=0,"",E46/D46*100)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B47" s="17" t="inlineStr">
+      <c r="B47" s="20" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D47" s="13" t="n">
+      <c r="C47" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D47" s="15" t="n">
         <v>36800</v>
       </c>
-      <c r="E47" s="13" t="n">
+      <c r="E47" s="15" t="n">
         <v>15200</v>
       </c>
-      <c r="F47" s="13">
+      <c r="F47" s="15">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="14">
+      <c r="G47" s="16">
         <f>IF(D47=0,"",E47/D47*100)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B48" s="20" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="n">
+      <c r="C48" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D48" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="13" t="n">
+      <c r="E48" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="13">
+      <c r="F48" s="15">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="14">
+      <c r="G48" s="16">
         <f>IF(D48=0,"",E48/D48*100)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B49" s="20" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C49" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="n">
+      <c r="C49" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D49" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="13" t="n">
+      <c r="E49" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="13">
+      <c r="F49" s="15">
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="14">
+      <c r="G49" s="16">
         <f>IF(D49=0,"",E49/D49*100)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="20" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B50" s="17" t="inlineStr">
+      <c r="B50" s="20" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D50" s="13" t="n">
+      <c r="C50" s="20" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D50" s="15" t="n">
         <v>6200</v>
       </c>
-      <c r="E50" s="13" t="n">
+      <c r="E50" s="15" t="n">
         <v>2600</v>
       </c>
-      <c r="F50" s="13">
+      <c r="F50" s="15">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="14">
+      <c r="G50" s="16">
         <f>IF(D50=0,"",E50/D50*100)</f>
         <v/>
       </c>

--- a/media/exports/reports/2025-12/funding.xlsx
+++ b/media/exports/reports/2025-12/funding.xlsx
@@ -12,7 +12,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="Cheapest_to_raise_Grants">'Report'!$B$51</definedName>
+    <definedName name="Dearest_to_raise_Fundraising_events">'Report'!$B$52</definedName>
+    <definedName name="Raised_year_to_date">'Report'!$B$53</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$E$61</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -127,15 +133,17 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -224,6 +232,357 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Cost to raise a dollar, by source, December 2025 (cents)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Cost to raise a dollar</v>
+          </tx>
+          <spPr>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:srgbClr val="0E9F6E"/>
+            </a:solidFill>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <invertIfNegative val="0"/>
+          <dLbls>
+            <numFmt formatCode="0&quot;¢&quot;"/>
+            <showLegendKey val="0"/>
+            <showVal val="1"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <cat>
+            <numRef>
+              <f>'Report'!$A$10:$A$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Report'!$B$10:$B$12</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="60"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="maxMin"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="l"/>
+        <numFmt formatCode="0&quot;¢&quot;" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Raised by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Grants</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$6:$D$20</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Donations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$21:$D$35</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Fundraising events</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data'!$B$6:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data'!$D$36:$D$50</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>8</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="1980000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="funding_Data" displayName="funding_Data" ref="A5:G50" headerRowCount="1">
+  <autoFilter ref="A5:G50"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Source"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Raised"/>
+    <tableColumn id="5" name="Cost of raising it"/>
+    <tableColumn id="6" name="Left after costs"/>
+    <tableColumn id="7" name="Cents per $1"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,7 +874,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -535,14 +894,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -573,7 +932,7 @@
       <c r="A9" s="6" t="inlineStr"/>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Value</t>
+          <t>Cost to raise a dollar</t>
         </is>
       </c>
     </row>
@@ -608,367 +967,377 @@
       </c>
     </row>
     <row r="13"/>
-    <row r="14">
-      <c r="A14" s="9" t="inlineStr">
+    <row r="14"/>
+    <row r="15"/>
+    <row r="16"/>
+    <row r="17"/>
+    <row r="18"/>
+    <row r="19"/>
+    <row r="20"/>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="3" t="inlineStr">
+    <row r="23" ht="30" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>In December it cost: Grants 10¢, donations 17¢ and fundraising events 42¢ to raise each dollar.</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" s="9" t="inlineStr">
+    <row r="24"/>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>Cheapest to raise in December: grants (10¢ a dollar). Dearest: fundraising events (42¢). Events are worth counting for what else they bring too (new donors, profile).</t>
         </is>
       </c>
     </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="27"/>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Source: Grants</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="9" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="3" t="inlineStr">
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="3" t="inlineStr">
         <is>
           <t>Grants: $390,886 raised this financial year to date (72.3% of everything raised), $42,600 to raise it, so $348,286 left for programs: 11¢ per dollar.</t>
         </is>
       </c>
     </row>
-    <row r="23"/>
-    <row r="24">
-      <c r="A24" s="9" t="inlineStr">
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>Most of the money, and usually the cheapest to raise, starting with grants that renew.</t>
         </is>
       </c>
     </row>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>Source: Donations</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="3" t="inlineStr">
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>Donations: $106,600 raised this financial year to date (19.7% of everything raised), $16,300 to raise it, so $90,300 left for programs: 15¢ per dollar.</t>
         </is>
       </c>
     </row>
-    <row r="30"/>
-    <row r="31">
-      <c r="A31" s="9" t="inlineStr">
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
+    <row r="40" ht="30" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
         <is>
           <t>Cheap and flexible (untied): the money that builds reserves.</t>
         </is>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>Source: Fundraising events</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>Fundraising events: $43,000 raised this financial year to date (8.0% of everything raised), $17,800 to raise it, so $25,200 left for programs: 41¢ per dollar.</t>
         </is>
       </c>
     </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="9" t="inlineStr">
+    <row r="45"/>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="3" t="inlineStr">
+    <row r="47" ht="30" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>The dearest per dollar: worth measuring the new donors each event brings in too.</t>
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="48"/>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>Every source at once</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C42" s="7" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>Compared with</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>Cheapest to raise: Grants</t>
         </is>
       </c>
-      <c r="B43" s="8">
+      <c r="B51" s="8">
         <f>Workings!B30</f>
         <v/>
       </c>
-      <c r="C43" s="10" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
         <is>
           <t>per $1 raised in December</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>Dearest to raise: Fundraising events</t>
         </is>
       </c>
-      <c r="B44" s="8">
+      <c r="B52" s="8">
         <f>Workings!B44</f>
         <v/>
       </c>
-      <c r="C44" s="10" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>per $1 raised in December</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Raised, year to date</t>
         </is>
       </c>
-      <c r="B45" s="11">
+      <c r="B53" s="11">
         <f>Workings!B53</f>
         <v/>
       </c>
-      <c r="C45" s="10" t="inlineStr">
+      <c r="C53" s="10" t="inlineStr">
         <is>
           <t>Jul to Dec 2025</t>
         </is>
       </c>
     </row>
-    <row r="46"/>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+    <row r="54"/>
+    <row r="55">
+      <c r="A55" s="12" t="inlineStr">
+        <is>
+          <t>Raised and left after costs, by month: every month is on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Financial year to date (Jul to Dec 2025), by source</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="6" t="inlineStr"/>
-      <c r="B48" s="7" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr"/>
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>Raised</t>
         </is>
       </c>
-      <c r="C48" s="7" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>Cost of raising it</t>
         </is>
       </c>
-      <c r="D48" s="7" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Left after costs</t>
         </is>
       </c>
-      <c r="E48" s="7" t="inlineStr">
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>Cost per $1</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="12" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B49" s="13" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>$390,886</t>
         </is>
       </c>
-      <c r="C49" s="13" t="inlineStr">
+      <c r="C59" s="14" t="inlineStr">
         <is>
           <t>$42,600</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
+      <c r="D59" s="14" t="inlineStr">
         <is>
           <t>$348,286</t>
         </is>
       </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="E59" s="14" t="inlineStr">
         <is>
           <t>11¢</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="12" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B50" s="13" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>$106,600</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C60" s="14" t="inlineStr">
         <is>
           <t>$16,300</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D60" s="14" t="inlineStr">
         <is>
           <t>$90,300</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E60" s="14" t="inlineStr">
         <is>
           <t>15¢</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="12" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B51" s="13" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>$43,000</t>
         </is>
       </c>
-      <c r="C51" s="13" t="inlineStr">
+      <c r="C61" s="14" t="inlineStr">
         <is>
           <t>$17,800</t>
         </is>
       </c>
-      <c r="D51" s="13" t="inlineStr">
+      <c r="D61" s="14" t="inlineStr">
         <is>
           <t>$25,200</t>
         </is>
       </c>
-      <c r="E51" s="13" t="inlineStr">
+      <c r="E61" s="14" t="inlineStr">
         <is>
           <t>41¢</t>
         </is>
       </c>
     </row>
-    <row r="52"/>
-    <row r="53">
-      <c r="A53" s="14" t="inlineStr">
-        <is>
-          <t>Raised and left after costs, by month: every month is on the Data sheet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
-    <row r="55"/>
+    <row r="62"/>
+    <row r="63"/>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A25:D25"/>
-    <mergeCell ref="A32:D32"/>
-    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A47:D47"/>
+    <mergeCell ref="A44:D44"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
-  <rowBreaks count="1" manualBreakCount="1">
-    <brk id="27" min="0" max="16383" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
+    <brk id="28" min="0" max="16383" man="1"/>
+    <brk id="49" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -997,14 +1366,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1386,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="14" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Fundraising cost ÷ money raised, for each source, in cents</t>
         </is>
@@ -1134,7 +1503,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
         <is>
           <t>Fundraising cost ÷ money raised, for each source, in cents</t>
         </is>
@@ -1251,7 +1620,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>Fundraising cost ÷ money raised, for each source, in cents</t>
         </is>
@@ -1368,7 +1737,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="12" t="inlineStr">
         <is>
           <t>Grants + donations + fundraising events</t>
         </is>
@@ -1432,7 +1801,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1472,14 +1841,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>Sample Community Services Ltd · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026)</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
         </is>
       </c>
     </row>
@@ -2922,7 +3291,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2931,5 +3300,9 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="20" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/media/exports/reports/2025-12/funding.xlsx
+++ b/media/exports/reports/2025-12/funding.xlsx
@@ -12,10 +12,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="Cheapest_to_raise_Grants">'Report'!$B$51</definedName>
-    <definedName name="Dearest_to_raise_Fundraising_events">'Report'!$B$52</definedName>
-    <definedName name="Raised_year_to_date">'Report'!$B$53</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$E$61</definedName>
+    <definedName name="Cheapest_to_raise_Grants">'Report'!$B$52</definedName>
+    <definedName name="Dearest_to_raise_Fundraising_events">'Report'!$B$53</definedName>
+    <definedName name="Raised_year_to_date">'Report'!$B$54</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$E$62</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$53</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Data'!$A$1:$G$50</definedName>
@@ -54,13 +54,13 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="002F7A5D"/>
-      <sz val="12"/>
+      <color rgb="0025342A"/>
     </font>
     <font>
       <name val="Roboto"/>
       <b val="1"/>
-      <color rgb="0025342A"/>
+      <color rgb="002F7A5D"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -116,15 +116,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -298,12 +301,12 @@
           </dLbls>
           <cat>
             <numRef>
-              <f>'Report'!$A$10:$A$12</f>
+              <f>'Report'!$A$11:$A$13</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Report'!$B$10:$B$12</f>
+              <f>'Report'!$B$11:$B$13</f>
             </numRef>
           </val>
         </ser>
@@ -521,7 +524,7 @@
     <from>
       <col>5</col>
       <colOff>0</colOff>
-      <row>8</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5400000" cy="1980000"/>
@@ -874,7 +877,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E63"/>
+  <dimension ref="A1:E64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -901,7 +904,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
@@ -909,64 +912,70 @@
     <row r="5" ht="32" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
+          <t>In short: Grants cost 10¢ to raise each dollar in December; fundraising events 42¢.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
           <t>Each source of money compared on what it raises and what it costs to raise. Pick a source and every chart, table row and note follows it.</t>
         </is>
       </c>
     </row>
-    <row r="6"/>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>Source: All sources</t>
-        </is>
-      </c>
-    </row>
+    <row r="7"/>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
+          <t>Source: All sources</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
           <t>Cost to raise a dollar, by source, December 2025 (cents)</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr"/>
-      <c r="B9" s="7" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="7" t="inlineStr"/>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>Cost to raise a dollar</t>
         </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Grants</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Donations</t>
-        </is>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>17</v>
+          <t>Grants</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>Donations</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B12" s="8" t="n">
+      <c r="B13" s="9" t="n">
         <v>42</v>
       </c>
     </row>
-    <row r="13"/>
     <row r="14"/>
     <row r="15"/>
     <row r="16"/>
@@ -975,198 +984,183 @@
     <row r="19"/>
     <row r="20"/>
     <row r="21"/>
-    <row r="22">
-      <c r="A22" s="9" t="inlineStr">
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>In December it cost: Grants 10¢, donations 17¢ and fundraising events 42¢ to raise each dollar.</t>
         </is>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="9" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Cheapest to raise in December: grants (10¢ a dollar). Dearest: fundraising events (42¢). Events are worth counting for what else they bring too (new donors, profile).</t>
         </is>
       </c>
     </row>
-    <row r="27"/>
-    <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Source: Grants</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="9" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="3" t="inlineStr">
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>Grants: $390,886 raised this financial year to date (72.3% of everything raised), $42,600 to raise it, so $348,286 left for programs: 11¢ per dollar.</t>
         </is>
       </c>
     </row>
-    <row r="31"/>
-    <row r="32">
-      <c r="A32" s="9" t="inlineStr">
+    <row r="32"/>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="3" t="inlineStr">
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>Most of the money, and usually the cheapest to raise, starting with grants that renew.</t>
         </is>
       </c>
     </row>
-    <row r="34"/>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Source: Donations</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="9" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>Donations: $106,600 raised this financial year to date (19.7% of everything raised), $16,300 to raise it, so $90,300 left for programs: 15¢ per dollar.</t>
         </is>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39">
-      <c r="A39" s="9" t="inlineStr">
+    <row r="39"/>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="3" t="inlineStr">
+    <row r="41" ht="30" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>Cheap and flexible (untied): the money that builds reserves.</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
-    <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+    <row r="42"/>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Source: Fundraising events</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="9" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>What it shows</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="3" t="inlineStr">
+    <row r="45" ht="30" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>Fundraising events: $43,000 raised this financial year to date (8.0% of everything raised), $17,800 to raise it, so $25,200 left for programs: 41¢ per dollar.</t>
         </is>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46">
-      <c r="A46" s="9" t="inlineStr">
+    <row r="46"/>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
         <is>
           <t>What you'd do about it</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
+    <row r="48" ht="30" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>The dearest per dollar: worth measuring the new donors each event brings in too.</t>
         </is>
       </c>
     </row>
-    <row r="48"/>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>Every source at once</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Headline number</t>
         </is>
       </c>
-      <c r="B50" s="7" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
-      <c r="C50" s="7" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>Compared with</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Cheapest to raise: Grants</t>
-        </is>
-      </c>
-      <c r="B51" s="8">
-        <f>Workings!B30</f>
-        <v/>
-      </c>
-      <c r="C51" s="10" t="inlineStr">
-        <is>
-          <t>per $1 raised in December</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Dearest to raise: Fundraising events</t>
-        </is>
-      </c>
-      <c r="B52" s="8">
-        <f>Workings!B44</f>
-        <v/>
-      </c>
-      <c r="C52" s="10" t="inlineStr">
+          <t>Cheapest to raise: Grants</t>
+        </is>
+      </c>
+      <c r="B52" s="9">
+        <f>Workings!B28</f>
+        <v/>
+      </c>
+      <c r="C52" s="11" t="inlineStr">
         <is>
           <t>per $1 raised in December</t>
         </is>
@@ -1175,159 +1169,176 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>Dearest to raise: Fundraising events</t>
+        </is>
+      </c>
+      <c r="B53" s="9">
+        <f>Workings!B44</f>
+        <v/>
+      </c>
+      <c r="C53" s="11" t="inlineStr">
+        <is>
+          <t>per $1 raised in December</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
           <t>Raised, year to date</t>
         </is>
       </c>
-      <c r="B53" s="11">
+      <c r="B54" s="12">
         <f>Workings!B53</f>
         <v/>
       </c>
-      <c r="C53" s="10" t="inlineStr">
+      <c r="C54" s="11" t="inlineStr">
         <is>
           <t>Jul to Dec 2025</t>
         </is>
       </c>
     </row>
-    <row r="54"/>
-    <row r="55">
-      <c r="A55" s="12" t="inlineStr">
+    <row r="55"/>
+    <row r="56">
+      <c r="A56" s="13" t="inlineStr">
         <is>
           <t>Raised and left after costs, by month: every month is on the Data sheet.</t>
         </is>
       </c>
     </row>
-    <row r="56"/>
-    <row r="57">
-      <c r="A57" s="5" t="inlineStr">
+    <row r="57"/>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
         <is>
           <t>Financial year to date (Jul to Dec 2025), by source</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr"/>
-      <c r="B58" s="7" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="7" t="inlineStr"/>
+      <c r="B59" s="8" t="inlineStr">
         <is>
           <t>Raised</t>
         </is>
       </c>
-      <c r="C58" s="7" t="inlineStr">
+      <c r="C59" s="8" t="inlineStr">
         <is>
           <t>Cost of raising it</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
+      <c r="D59" s="8" t="inlineStr">
         <is>
           <t>Left after costs</t>
         </is>
       </c>
-      <c r="E58" s="7" t="inlineStr">
+      <c r="E59" s="8" t="inlineStr">
         <is>
           <t>Cost per $1</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="14" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
         <is>
           <t>$390,886</t>
         </is>
       </c>
-      <c r="C59" s="14" t="inlineStr">
+      <c r="C60" s="15" t="inlineStr">
         <is>
           <t>$42,600</t>
         </is>
       </c>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D60" s="15" t="inlineStr">
         <is>
           <t>$348,286</t>
         </is>
       </c>
-      <c r="E59" s="14" t="inlineStr">
+      <c r="E60" s="15" t="inlineStr">
         <is>
           <t>11¢</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="13" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="14" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B61" s="15" t="inlineStr">
         <is>
           <t>$106,600</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr">
+      <c r="C61" s="15" t="inlineStr">
         <is>
           <t>$16,300</t>
         </is>
       </c>
-      <c r="D60" s="14" t="inlineStr">
+      <c r="D61" s="15" t="inlineStr">
         <is>
           <t>$90,300</t>
         </is>
       </c>
-      <c r="E60" s="14" t="inlineStr">
+      <c r="E61" s="15" t="inlineStr">
         <is>
           <t>15¢</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="14" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B61" s="14" t="inlineStr">
+      <c r="B62" s="15" t="inlineStr">
         <is>
           <t>$43,000</t>
         </is>
       </c>
-      <c r="C61" s="14" t="inlineStr">
+      <c r="C62" s="15" t="inlineStr">
         <is>
           <t>$17,800</t>
         </is>
       </c>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="D62" s="15" t="inlineStr">
         <is>
           <t>$25,200</t>
         </is>
       </c>
-      <c r="E61" s="14" t="inlineStr">
+      <c r="E62" s="15" t="inlineStr">
         <is>
           <t>41¢</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
     <row r="63"/>
+    <row r="64"/>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A5:D5"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A30:D30"/>
-    <mergeCell ref="A33:D33"/>
-    <mergeCell ref="A47:D47"/>
-    <mergeCell ref="A44:D44"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A48:D48"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A41:D41"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1335,7 +1346,7 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="28" min="0" max="16383" man="1"/>
-    <brk id="49" min="0" max="16383" man="1"/>
+    <brk id="50" min="0" max="16383" man="1"/>
   </rowBreaks>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -1373,28 +1384,28 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, by source, December 2025</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Fundraising cost ÷ money raised, for each source, in cents</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr"/>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="A7" s="7" t="inlineStr"/>
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1406,7 +1417,7 @@
           <t>Grants: cost (grant writing and reporting)</t>
         </is>
       </c>
-      <c r="B8" s="15" t="n">
+      <c r="B8" s="16" t="n">
         <v>7100</v>
       </c>
     </row>
@@ -1416,7 +1427,7 @@
           <t>Grants: raised</t>
         </is>
       </c>
-      <c r="B9" s="15" t="n">
+      <c r="B9" s="16" t="n">
         <v>68793</v>
       </c>
     </row>
@@ -1426,7 +1437,7 @@
           <t>Donations: cost (donor campaigns)</t>
         </is>
       </c>
-      <c r="B10" s="15" t="n">
+      <c r="B10" s="16" t="n">
         <v>4400</v>
       </c>
     </row>
@@ -1436,7 +1447,7 @@
           <t>Donations: raised</t>
         </is>
       </c>
-      <c r="B11" s="15" t="n">
+      <c r="B11" s="16" t="n">
         <v>26100</v>
       </c>
     </row>
@@ -1446,7 +1457,7 @@
           <t>Fundraising events: cost (event costs)</t>
         </is>
       </c>
-      <c r="B12" s="15" t="n">
+      <c r="B12" s="16" t="n">
         <v>2600</v>
       </c>
     </row>
@@ -1456,7 +1467,7 @@
           <t>Fundraising events: raised</t>
         </is>
       </c>
-      <c r="B13" s="15" t="n">
+      <c r="B13" s="16" t="n">
         <v>6200</v>
       </c>
     </row>
@@ -1466,7 +1477,7 @@
           <t>Grants: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="17">
         <f>B8/B9*100</f>
         <v/>
       </c>
@@ -1477,18 +1488,18 @@
           <t>Donations: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="17">
         <f>B10/B11*100</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Fundraising events: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <f>B12/B13*100</f>
         <v/>
       </c>
@@ -1496,22 +1507,22 @@
     <row r="17"/>
     <row r="18"/>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, by source, December 2025</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Fundraising cost ÷ money raised, for each source, in cents</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr"/>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="A21" s="7" t="inlineStr"/>
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1523,7 +1534,7 @@
           <t>Grants: cost (grant writing and reporting)</t>
         </is>
       </c>
-      <c r="B22" s="15" t="n">
+      <c r="B22" s="16" t="n">
         <v>7100</v>
       </c>
     </row>
@@ -1533,7 +1544,7 @@
           <t>Grants: raised</t>
         </is>
       </c>
-      <c r="B23" s="15" t="n">
+      <c r="B23" s="16" t="n">
         <v>68793</v>
       </c>
     </row>
@@ -1543,7 +1554,7 @@
           <t>Donations: cost (donor campaigns)</t>
         </is>
       </c>
-      <c r="B24" s="15" t="n">
+      <c r="B24" s="16" t="n">
         <v>4400</v>
       </c>
     </row>
@@ -1553,7 +1564,7 @@
           <t>Donations: raised</t>
         </is>
       </c>
-      <c r="B25" s="15" t="n">
+      <c r="B25" s="16" t="n">
         <v>26100</v>
       </c>
     </row>
@@ -1563,7 +1574,7 @@
           <t>Fundraising events: cost (event costs)</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
+      <c r="B26" s="16" t="n">
         <v>2600</v>
       </c>
     </row>
@@ -1573,7 +1584,7 @@
           <t>Fundraising events: raised</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
+      <c r="B27" s="16" t="n">
         <v>6200</v>
       </c>
     </row>
@@ -1583,7 +1594,7 @@
           <t>Grants: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="17">
         <f>B22/B23*100</f>
         <v/>
       </c>
@@ -1594,18 +1605,18 @@
           <t>Donations: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="17">
         <f>B24/B25*100</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="18" t="inlineStr">
         <is>
           <t>Fundraising events: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B30" s="18">
+      <c r="B30" s="19">
         <f>B26/B27*100</f>
         <v/>
       </c>
@@ -1613,22 +1624,22 @@
     <row r="31"/>
     <row r="32"/>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Cost to raise a dollar, by source, December 2025</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>Fundraising cost ÷ money raised, for each source, in cents</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr"/>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="A35" s="7" t="inlineStr"/>
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>Dec 2025</t>
         </is>
@@ -1640,7 +1651,7 @@
           <t>Grants: cost (grant writing and reporting)</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
+      <c r="B36" s="16" t="n">
         <v>7100</v>
       </c>
     </row>
@@ -1650,7 +1661,7 @@
           <t>Grants: raised</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
+      <c r="B37" s="16" t="n">
         <v>68793</v>
       </c>
     </row>
@@ -1660,7 +1671,7 @@
           <t>Donations: cost (donor campaigns)</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
+      <c r="B38" s="16" t="n">
         <v>4400</v>
       </c>
     </row>
@@ -1670,7 +1681,7 @@
           <t>Donations: raised</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
+      <c r="B39" s="16" t="n">
         <v>26100</v>
       </c>
     </row>
@@ -1680,7 +1691,7 @@
           <t>Fundraising events: cost (event costs)</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
+      <c r="B40" s="16" t="n">
         <v>2600</v>
       </c>
     </row>
@@ -1690,7 +1701,7 @@
           <t>Fundraising events: raised</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
+      <c r="B41" s="16" t="n">
         <v>6200</v>
       </c>
     </row>
@@ -1700,7 +1711,7 @@
           <t>Grants: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="17">
         <f>B36/B37*100</f>
         <v/>
       </c>
@@ -1711,18 +1722,18 @@
           <t>Donations: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="17">
         <f>B38/B39*100</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="18" t="inlineStr">
         <is>
           <t>Fundraising events: cost per dollar raised</t>
         </is>
       </c>
-      <c r="B44" s="18">
+      <c r="B44" s="19">
         <f>B40/B41*100</f>
         <v/>
       </c>
@@ -1730,22 +1741,22 @@
     <row r="45"/>
     <row r="46"/>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Raised, financial year to date (Jul to Dec 2025)</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="12" t="inlineStr">
+      <c r="A48" s="13" t="inlineStr">
         <is>
           <t>Grants + donations + fundraising events</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="6" t="inlineStr"/>
-      <c r="B49" s="7" t="inlineStr">
+      <c r="A49" s="7" t="inlineStr"/>
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>Year to date</t>
         </is>
@@ -1757,7 +1768,7 @@
           <t>Grants, raised</t>
         </is>
       </c>
-      <c r="B50" s="15" t="n">
+      <c r="B50" s="16" t="n">
         <v>390886</v>
       </c>
     </row>
@@ -1767,7 +1778,7 @@
           <t>Donations, raised</t>
         </is>
       </c>
-      <c r="B51" s="15" t="n">
+      <c r="B51" s="16" t="n">
         <v>106600</v>
       </c>
     </row>
@@ -1777,17 +1788,17 @@
           <t>Fundraising events, raised</t>
         </is>
       </c>
-      <c r="B52" s="15" t="n">
+      <c r="B52" s="16" t="n">
         <v>43000</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="18" t="inlineStr">
         <is>
           <t>Raised, year to date</t>
         </is>
       </c>
-      <c r="B53" s="19">
+      <c r="B53" s="20">
         <f>B50+B51+B52</f>
         <v/>
       </c>
@@ -1801,7 +1812,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1848,1439 +1859,1439 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Period: December 2025 · Data status: Nov 2025 locked · Dec 2025 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 10 Oct 2026, 9:55pm</t>
         </is>
       </c>
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C5" s="7" t="inlineStr">
+      <c r="C5" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="D5" s="7" t="inlineStr">
+      <c r="D5" s="8" t="inlineStr">
         <is>
           <t>Raised</t>
         </is>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr">
         <is>
           <t>Cost of raising it</t>
         </is>
       </c>
-      <c r="F5" s="7" t="inlineStr">
+      <c r="F5" s="8" t="inlineStr">
         <is>
           <t>Left after costs</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>Cents per $1</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D6" s="15" t="n">
+      <c r="C6" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="n">
         <v>26600</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="16">
         <f>D6-E6</f>
         <v/>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="17">
         <f>IF(D6=0,"",E6/D6*100)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="20" t="inlineStr">
+      <c r="A7" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D7" s="15" t="n">
+      <c r="C7" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="n">
         <v>31800</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="16">
         <f>D7-E7</f>
         <v/>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="17">
         <f>IF(D7=0,"",E7/D7*100)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="20" t="inlineStr">
+      <c r="A8" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B8" s="20" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="n">
+      <c r="C8" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="n">
         <v>29700</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F8" s="15">
+      <c r="F8" s="16">
         <f>D8-E8</f>
         <v/>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="17">
         <f>IF(D8=0,"",E8/D8*100)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B9" s="20" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C9" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
+      <c r="C9" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D9" s="16" t="n">
         <v>62700</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F9" s="15">
+      <c r="F9" s="16">
         <f>D9-E9</f>
         <v/>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="17">
         <f>IF(D9=0,"",E9/D9*100)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="inlineStr">
+      <c r="A10" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
+      <c r="C10" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="n">
         <v>61700</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F10" s="15">
+      <c r="F10" s="16">
         <f>D10-E10</f>
         <v/>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="17">
         <f>IF(D10=0,"",E10/D10*100)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="20" t="inlineStr">
+      <c r="A11" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
+      <c r="C11" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="n">
         <v>54500</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F11" s="15">
+      <c r="F11" s="16">
         <f>D11-E11</f>
         <v/>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="17">
         <f>IF(D11=0,"",E11/D11*100)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="20" t="inlineStr">
+      <c r="A12" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B12" s="20" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
+      <c r="C12" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D12" s="16" t="n">
         <v>61500</v>
       </c>
-      <c r="E12" s="15" t="n">
+      <c r="E12" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F12" s="15">
+      <c r="F12" s="16">
         <f>D12-E12</f>
         <v/>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="17">
         <f>IF(D12=0,"",E12/D12*100)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="20" t="inlineStr">
+      <c r="A13" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B13" s="20" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
+      <c r="C13" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="n">
         <v>61700</v>
       </c>
-      <c r="E13" s="15" t="n">
+      <c r="E13" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F13" s="15">
+      <c r="F13" s="16">
         <f>D13-E13</f>
         <v/>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="17">
         <f>IF(D13=0,"",E13/D13*100)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="20" t="inlineStr">
+      <c r="A14" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B14" s="20" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D14" s="15" t="n">
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="n">
         <v>52200</v>
       </c>
-      <c r="E14" s="15" t="n">
+      <c r="E14" s="16" t="n">
         <v>6500</v>
       </c>
-      <c r="F14" s="15">
+      <c r="F14" s="16">
         <f>D14-E14</f>
         <v/>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="17">
         <f>IF(D14=0,"",E14/D14*100)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="20" t="inlineStr">
+      <c r="A15" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
+      <c r="C15" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D15" s="16" t="n">
         <v>59063</v>
       </c>
-      <c r="E15" s="15" t="n">
+      <c r="E15" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="F15" s="15">
+      <c r="F15" s="16">
         <f>D15-E15</f>
         <v/>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="17">
         <f>IF(D15=0,"",E15/D15*100)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="20" t="inlineStr">
+      <c r="A16" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n">
+      <c r="C16" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D16" s="16" t="n">
         <v>61544</v>
       </c>
-      <c r="E16" s="15" t="n">
+      <c r="E16" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="F16" s="15">
+      <c r="F16" s="16">
         <f>D16-E16</f>
         <v/>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="17">
         <f>IF(D16=0,"",E16/D16*100)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="20" t="inlineStr">
+      <c r="A17" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
+      <c r="C17" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D17" s="16" t="n">
         <v>62137</v>
       </c>
-      <c r="E17" s="15" t="n">
+      <c r="E17" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="F17" s="15">
+      <c r="F17" s="16">
         <f>D17-E17</f>
         <v/>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="17">
         <f>IF(D17=0,"",E17/D17*100)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="inlineStr">
+      <c r="A18" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="n">
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="n">
         <v>69185</v>
       </c>
-      <c r="E18" s="15" t="n">
+      <c r="E18" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="F18" s="15">
+      <c r="F18" s="16">
         <f>D18-E18</f>
         <v/>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="17">
         <f>IF(D18=0,"",E18/D18*100)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="20" t="inlineStr">
+      <c r="A19" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B19" s="20" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D19" s="15" t="n">
+      <c r="C19" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D19" s="16" t="n">
         <v>70164</v>
       </c>
-      <c r="E19" s="15" t="n">
+      <c r="E19" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="F19" s="15">
+      <c r="F19" s="16">
         <f>D19-E19</f>
         <v/>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="17">
         <f>IF(D19=0,"",E19/D19*100)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="inlineStr">
+      <c r="A20" s="21" t="inlineStr">
         <is>
           <t>Grants</t>
         </is>
       </c>
-      <c r="B20" s="20" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D20" s="15" t="n">
+      <c r="C20" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n">
         <v>68793</v>
       </c>
-      <c r="E20" s="15" t="n">
+      <c r="E20" s="16" t="n">
         <v>7100</v>
       </c>
-      <c r="F20" s="15">
+      <c r="F20" s="16">
         <f>D20-E20</f>
         <v/>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="17">
         <f>IF(D20=0,"",E20/D20*100)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="20" t="inlineStr">
+      <c r="A21" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C21" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D21" s="15" t="n">
+      <c r="C21" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D21" s="16" t="n">
         <v>15300</v>
       </c>
-      <c r="E21" s="15" t="n">
+      <c r="E21" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F21" s="15">
+      <c r="F21" s="16">
         <f>D21-E21</f>
         <v/>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="17">
         <f>IF(D21=0,"",E21/D21*100)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="20" t="inlineStr">
+      <c r="A22" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D22" s="15" t="n">
+      <c r="C22" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D22" s="16" t="n">
         <v>17700</v>
       </c>
-      <c r="E22" s="15" t="n">
+      <c r="E22" s="16" t="n">
         <v>3100</v>
       </c>
-      <c r="F22" s="15">
+      <c r="F22" s="16">
         <f>D22-E22</f>
         <v/>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="17">
         <f>IF(D22=0,"",E22/D22*100)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="20" t="inlineStr">
+      <c r="A23" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D23" s="15" t="n">
+      <c r="C23" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D23" s="16" t="n">
         <v>24700</v>
       </c>
-      <c r="E23" s="15" t="n">
+      <c r="E23" s="16" t="n">
         <v>4400</v>
       </c>
-      <c r="F23" s="15">
+      <c r="F23" s="16">
         <f>D23-E23</f>
         <v/>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="17">
         <f>IF(D23=0,"",E23/D23*100)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="20" t="inlineStr">
+      <c r="A24" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B24" s="20" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C24" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="n">
+      <c r="C24" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D24" s="16" t="n">
         <v>12400</v>
       </c>
-      <c r="E24" s="15" t="n">
+      <c r="E24" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F24" s="15">
+      <c r="F24" s="16">
         <f>D24-E24</f>
         <v/>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="17">
         <f>IF(D24=0,"",E24/D24*100)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="20" t="inlineStr">
+      <c r="A25" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B25" s="20" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C25" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="n">
+      <c r="C25" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="n">
         <v>15600</v>
       </c>
-      <c r="E25" s="15" t="n">
+      <c r="E25" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F25" s="15">
+      <c r="F25" s="16">
         <f>D25-E25</f>
         <v/>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="17">
         <f>IF(D25=0,"",E25/D25*100)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="20" t="inlineStr">
+      <c r="A26" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C26" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="n">
+      <c r="C26" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D26" s="16" t="n">
         <v>15700</v>
       </c>
-      <c r="E26" s="15" t="n">
+      <c r="E26" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F26" s="15">
+      <c r="F26" s="16">
         <f>D26-E26</f>
         <v/>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="17">
         <f>IF(D26=0,"",E26/D26*100)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="20" t="inlineStr">
+      <c r="A27" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B27" s="20" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C27" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="n">
+      <c r="C27" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="n">
         <v>15700</v>
       </c>
-      <c r="E27" s="15" t="n">
+      <c r="E27" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F27" s="15">
+      <c r="F27" s="16">
         <f>D27-E27</f>
         <v/>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="17">
         <f>IF(D27=0,"",E27/D27*100)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="20" t="inlineStr">
+      <c r="A28" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D28" s="15" t="n">
+      <c r="C28" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D28" s="16" t="n">
         <v>15800</v>
       </c>
-      <c r="E28" s="15" t="n">
+      <c r="E28" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F28" s="15">
+      <c r="F28" s="16">
         <f>D28-E28</f>
         <v/>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="17">
         <f>IF(D28=0,"",E28/D28*100)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="20" t="inlineStr">
+      <c r="A29" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B29" s="20" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C29" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D29" s="15" t="n">
+      <c r="C29" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="n">
         <v>38100</v>
       </c>
-      <c r="E29" s="15" t="n">
+      <c r="E29" s="16" t="n">
         <v>5500</v>
       </c>
-      <c r="F29" s="15">
+      <c r="F29" s="16">
         <f>D29-E29</f>
         <v/>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="17">
         <f>IF(D29=0,"",E29/D29*100)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="20" t="inlineStr">
+      <c r="A30" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B30" s="20" t="inlineStr">
+      <c r="B30" s="21" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C30" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D30" s="15" t="n">
+      <c r="C30" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="n">
         <v>13500</v>
       </c>
-      <c r="E30" s="15" t="n">
+      <c r="E30" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F30" s="15">
+      <c r="F30" s="16">
         <f>D30-E30</f>
         <v/>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="17">
         <f>IF(D30=0,"",E30/D30*100)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="20" t="inlineStr">
+      <c r="A31" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B31" s="20" t="inlineStr">
+      <c r="B31" s="21" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C31" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="n">
+      <c r="C31" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="n">
         <v>16000</v>
       </c>
-      <c r="E31" s="15" t="n">
+      <c r="E31" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="16">
         <f>D31-E31</f>
         <v/>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="17">
         <f>IF(D31=0,"",E31/D31*100)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="20" t="inlineStr">
+      <c r="A32" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B32" s="20" t="inlineStr">
+      <c r="B32" s="21" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C32" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="n">
+      <c r="C32" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D32" s="16" t="n">
         <v>16100</v>
       </c>
-      <c r="E32" s="15" t="n">
+      <c r="E32" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F32" s="15">
+      <c r="F32" s="16">
         <f>D32-E32</f>
         <v/>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="17">
         <f>IF(D32=0,"",E32/D32*100)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="20" t="inlineStr">
+      <c r="A33" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B33" s="20" t="inlineStr">
+      <c r="B33" s="21" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C33" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D33" s="15" t="n">
+      <c r="C33" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="n">
         <v>16200</v>
       </c>
-      <c r="E33" s="15" t="n">
+      <c r="E33" s="16" t="n">
         <v>2200</v>
       </c>
-      <c r="F33" s="15">
+      <c r="F33" s="16">
         <f>D33-E33</f>
         <v/>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="17">
         <f>IF(D33=0,"",E33/D33*100)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="20" t="inlineStr">
+      <c r="A34" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B34" s="20" t="inlineStr">
+      <c r="B34" s="21" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C34" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="n">
+      <c r="C34" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D34" s="16" t="n">
         <v>18700</v>
       </c>
-      <c r="E34" s="15" t="n">
+      <c r="E34" s="16" t="n">
         <v>3100</v>
       </c>
-      <c r="F34" s="15">
+      <c r="F34" s="16">
         <f>D34-E34</f>
         <v/>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="17">
         <f>IF(D34=0,"",E34/D34*100)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="20" t="inlineStr">
+      <c r="A35" s="21" t="inlineStr">
         <is>
           <t>Donations</t>
         </is>
       </c>
-      <c r="B35" s="20" t="inlineStr">
+      <c r="B35" s="21" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C35" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D35" s="15" t="n">
+      <c r="C35" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="n">
         <v>26100</v>
       </c>
-      <c r="E35" s="15" t="n">
+      <c r="E35" s="16" t="n">
         <v>4400</v>
       </c>
-      <c r="F35" s="15">
+      <c r="F35" s="16">
         <f>D35-E35</f>
         <v/>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="17">
         <f>IF(D35=0,"",E35/D35*100)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="20" t="inlineStr">
+      <c r="A36" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B36" s="20" t="inlineStr">
+      <c r="B36" s="21" t="inlineStr">
         <is>
           <t>Oct 24</t>
         </is>
       </c>
-      <c r="C36" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="n">
+      <c r="C36" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E36" s="15" t="n">
+      <c r="E36" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="15">
+      <c r="F36" s="16">
         <f>D36-E36</f>
         <v/>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="17">
         <f>IF(D36=0,"",E36/D36*100)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="20" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B37" s="20" t="inlineStr">
+      <c r="B37" s="21" t="inlineStr">
         <is>
           <t>Nov 24</t>
         </is>
       </c>
-      <c r="C37" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D37" s="15" t="n">
+      <c r="C37" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E37" s="15" t="n">
+      <c r="E37" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="15">
+      <c r="F37" s="16">
         <f>D37-E37</f>
         <v/>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="17">
         <f>IF(D37=0,"",E37/D37*100)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="20" t="inlineStr">
+      <c r="A38" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B38" s="20" t="inlineStr">
+      <c r="B38" s="21" t="inlineStr">
         <is>
           <t>Dec 24</t>
         </is>
       </c>
-      <c r="C38" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D38" s="15" t="n">
+      <c r="C38" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="n">
         <v>6200</v>
       </c>
-      <c r="E38" s="15" t="n">
+      <c r="E38" s="16" t="n">
         <v>2600</v>
       </c>
-      <c r="F38" s="15">
+      <c r="F38" s="16">
         <f>D38-E38</f>
         <v/>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="17">
         <f>IF(D38=0,"",E38/D38*100)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="20" t="inlineStr">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B39" s="20" t="inlineStr">
+      <c r="B39" s="21" t="inlineStr">
         <is>
           <t>Jan 25</t>
         </is>
       </c>
-      <c r="C39" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D39" s="15" t="n">
+      <c r="C39" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E39" s="15" t="n">
+      <c r="E39" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="15">
+      <c r="F39" s="16">
         <f>D39-E39</f>
         <v/>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="17">
         <f>IF(D39=0,"",E39/D39*100)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="20" t="inlineStr">
+      <c r="A40" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B40" s="20" t="inlineStr">
+      <c r="B40" s="21" t="inlineStr">
         <is>
           <t>Feb 25</t>
         </is>
       </c>
-      <c r="C40" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D40" s="15" t="n">
+      <c r="C40" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E40" s="15" t="n">
+      <c r="E40" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="15">
+      <c r="F40" s="16">
         <f>D40-E40</f>
         <v/>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="17">
         <f>IF(D40=0,"",E40/D40*100)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="20" t="inlineStr">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B41" s="20" t="inlineStr">
+      <c r="B41" s="21" t="inlineStr">
         <is>
           <t>Mar 25</t>
         </is>
       </c>
-      <c r="C41" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D41" s="15" t="n">
+      <c r="C41" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E41" s="15" t="n">
+      <c r="E41" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="15">
+      <c r="F41" s="16">
         <f>D41-E41</f>
         <v/>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="17">
         <f>IF(D41=0,"",E41/D41*100)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="20" t="inlineStr">
+      <c r="A42" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B42" s="20" t="inlineStr">
+      <c r="B42" s="21" t="inlineStr">
         <is>
           <t>Apr 25</t>
         </is>
       </c>
-      <c r="C42" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D42" s="15" t="n">
+      <c r="C42" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E42" s="15" t="n">
+      <c r="E42" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="15">
+      <c r="F42" s="16">
         <f>D42-E42</f>
         <v/>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="17">
         <f>IF(D42=0,"",E42/D42*100)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="20" t="inlineStr">
+      <c r="A43" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B43" s="20" t="inlineStr">
+      <c r="B43" s="21" t="inlineStr">
         <is>
           <t>May 25</t>
         </is>
       </c>
-      <c r="C43" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D43" s="15" t="n">
+      <c r="C43" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E43" s="15" t="n">
+      <c r="E43" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="15">
+      <c r="F43" s="16">
         <f>D43-E43</f>
         <v/>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="17">
         <f>IF(D43=0,"",E43/D43*100)</f>
         <v/>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="20" t="inlineStr">
+      <c r="A44" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B44" s="20" t="inlineStr">
+      <c r="B44" s="21" t="inlineStr">
         <is>
           <t>Jun 25</t>
         </is>
       </c>
-      <c r="C44" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D44" s="15" t="n">
+      <c r="C44" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E44" s="15" t="n">
+      <c r="E44" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="15">
+      <c r="F44" s="16">
         <f>D44-E44</f>
         <v/>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="17">
         <f>IF(D44=0,"",E44/D44*100)</f>
         <v/>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="20" t="inlineStr">
+      <c r="A45" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B45" s="20" t="inlineStr">
+      <c r="B45" s="21" t="inlineStr">
         <is>
           <t>Jul 25</t>
         </is>
       </c>
-      <c r="C45" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D45" s="15" t="n">
+      <c r="C45" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E45" s="15" t="n">
+      <c r="E45" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="15">
+      <c r="F45" s="16">
         <f>D45-E45</f>
         <v/>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="17">
         <f>IF(D45=0,"",E45/D45*100)</f>
         <v/>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="20" t="inlineStr">
+      <c r="A46" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B46" s="20" t="inlineStr">
+      <c r="B46" s="21" t="inlineStr">
         <is>
           <t>Aug 25</t>
         </is>
       </c>
-      <c r="C46" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D46" s="15" t="n">
+      <c r="C46" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E46" s="15" t="n">
+      <c r="E46" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="15">
+      <c r="F46" s="16">
         <f>D46-E46</f>
         <v/>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="17">
         <f>IF(D46=0,"",E46/D46*100)</f>
         <v/>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="20" t="inlineStr">
+      <c r="A47" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B47" s="20" t="inlineStr">
+      <c r="B47" s="21" t="inlineStr">
         <is>
           <t>Sep 25</t>
         </is>
       </c>
-      <c r="C47" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D47" s="15" t="n">
+      <c r="C47" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="n">
         <v>36800</v>
       </c>
-      <c r="E47" s="15" t="n">
+      <c r="E47" s="16" t="n">
         <v>15200</v>
       </c>
-      <c r="F47" s="15">
+      <c r="F47" s="16">
         <f>D47-E47</f>
         <v/>
       </c>
-      <c r="G47" s="16">
+      <c r="G47" s="17">
         <f>IF(D47=0,"",E47/D47*100)</f>
         <v/>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="20" t="inlineStr">
+      <c r="A48" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B48" s="20" t="inlineStr">
+      <c r="B48" s="21" t="inlineStr">
         <is>
           <t>Oct 25</t>
         </is>
       </c>
-      <c r="C48" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D48" s="15" t="n">
+      <c r="C48" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E48" s="15" t="n">
+      <c r="E48" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="15">
+      <c r="F48" s="16">
         <f>D48-E48</f>
         <v/>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="17">
         <f>IF(D48=0,"",E48/D48*100)</f>
         <v/>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="20" t="inlineStr">
+      <c r="A49" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B49" s="20" t="inlineStr">
+      <c r="B49" s="21" t="inlineStr">
         <is>
           <t>Nov 25</t>
         </is>
       </c>
-      <c r="C49" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D49" s="15" t="n">
+      <c r="C49" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D49" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="E49" s="15" t="n">
+      <c r="E49" s="16" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="15">
+      <c r="F49" s="16">
         <f>D49-E49</f>
         <v/>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="17">
         <f>IF(D49=0,"",E49/D49*100)</f>
         <v/>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="20" t="inlineStr">
+      <c r="A50" s="21" t="inlineStr">
         <is>
           <t>Fundraising events</t>
         </is>
       </c>
-      <c r="B50" s="20" t="inlineStr">
+      <c r="B50" s="21" t="inlineStr">
         <is>
           <t>Dec 25</t>
         </is>
       </c>
-      <c r="C50" s="20" t="inlineStr">
-        <is>
-          <t>Locked</t>
-        </is>
-      </c>
-      <c r="D50" s="15" t="n">
+      <c r="C50" s="21" t="inlineStr">
+        <is>
+          <t>Locked</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="n">
         <v>6200</v>
       </c>
-      <c r="E50" s="15" t="n">
+      <c r="E50" s="16" t="n">
         <v>2600</v>
       </c>
-      <c r="F50" s="15">
+      <c r="F50" s="16">
         <f>D50-E50</f>
         <v/>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="17">
         <f>IF(D50=0,"",E50/D50*100)</f>
         <v/>
       </c>
@@ -3291,7 +3302,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Community Services Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 funding.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 10 Oct 2026, 9:55pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
